--- a/pipelines/Demo_data/Templates/group_export_template.xlsx
+++ b/pipelines/Demo_data/Templates/group_export_template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t xml:space="preserve">Групповой отчёт</t>
   </si>
@@ -67,7 +67,7 @@
     <t>{{row.Итого}}</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;- Для табличного вывода можно применять плайсхолдеры , но в настройках вывода таблицы, все равно нужно явно кузывать номер столбца для вывода</t>
+    <t xml:space="preserve">&lt;- Для табличного вывода можно применять плайсхолдеры , но в настройках вывода таблицы, все равно нужно явно указывать номер столбца для вывода</t>
   </si>
   <si>
     <t xml:space="preserve">Строк: {{agg.lines_count}}</t>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t xml:space="preserve"> {{agg.to_nds}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Список лотов поставки: {{agg.lot}}</t>
   </si>
 </sst>
 </file>
@@ -177,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="160" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="0" pivotButton="0"/>
@@ -202,6 +205,7 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="161" xfId="0" applyNumberFormat="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -815,14 +819,14 @@
       <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>21</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="J10" s="13" t="s">
+      <c r="H10" s="13"/>
+      <c r="J10" s="14" t="s">
         <v>23</v>
       </c>
     </row>
@@ -831,14 +835,15 @@
     <row r="13" ht="14.25">
       <c r="A13" s="10"/>
     </row>
+    <row r="14" ht="14.25">
+      <c r="C14" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="16" ht="14.25">
       <c r="E16" s="10"/>
     </row>
-    <row r="27" ht="14.25">
-      <c r="I27" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
+    <row r="27" ht="14.25"/>
     <row r="32" ht="14.25">
       <c r="A32" s="11" t="s">
         <v>19</v>

--- a/pipelines/Demo_data/Templates/group_export_template.xlsx
+++ b/pipelines/Demo_data/Templates/group_export_template.xlsx
@@ -222,6 +222,1356 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" cap="all">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="50"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.222640"/>
+          <c:y val="0.069930"/>
+          <c:w val="0.430070"/>
+          <c:h val="0.718790"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$9:$D$10</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:dLblPos val="inEnd"/>
+              <c:layout/>
+              <c:showBubbleSize val="0"/>
+              <c:showCatName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showPercent val="0"/>
+              <c:showSerName val="0"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:dLblPos val="inEnd"/>
+              <c:layout/>
+              <c:showBubbleSize val="0"/>
+              <c:showCatName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showPercent val="0"/>
+              <c:showSerName val="0"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:dLblPos val="inEnd"/>
+              <c:layout/>
+              <c:showBubbleSize val="0"/>
+              <c:showCatName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showPercent val="0"/>
+              <c:showSerName val="0"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:dLblPos val="inEnd"/>
+              <c:layout/>
+              <c:showBubbleSize val="0"/>
+              <c:showCatName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showPercent val="0"/>
+              <c:showSerName val="0"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:dLblPos val="inEnd"/>
+              <c:layout/>
+              <c:showBubbleSize val="0"/>
+              <c:showCatName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showPercent val="0"/>
+              <c:showSerName val="0"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:dLblPos val="inEnd"/>
+              <c:layout/>
+              <c:showBubbleSize val="0"/>
+              <c:showCatName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showPercent val="0"/>
+              <c:showSerName val="0"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:dLblPos val="inEnd"/>
+              <c:layout/>
+              <c:showBubbleSize val="0"/>
+              <c:showCatName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showPercent val="0"/>
+              <c:showSerName val="0"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
+            </c:dLbl>
+            <c:dLblPos val="inEnd"/>
+            <c:showBubbleSize val="0"/>
+            <c:showCatName val="1"/>
+            <c:showLeaderLines val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showPercent val="0"/>
+            <c:showSerName val="0"/>
+            <c:showVal val="0"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="90000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:txPr>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$9:$B$18</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$11:$D$17</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="1"/>
+          <c:showLeaderLines val="1"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="90000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr/>
+            </a:p>
+          </c:txPr>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm>
+      <a:off x="6496049" y="3081337"/>
+      <a:ext cx="4552949" cy="2724149"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="263">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="90000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" rotWithShape="0">
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+            <a:alpha val="40000"/>
+          </a:schemeClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="90000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" cap="all"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="15875" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" spc="19"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>209549</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>133349</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="558292630" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6496049" y="3081337"/>
+        <a:ext cx="4552949" cy="2724149"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
@@ -854,5 +2204,6 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>